--- a/LYTS.xlsx
+++ b/LYTS.xlsx
@@ -1,150 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dillonwalton/Desktop/business/models/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACEDE9A8-8DC0-FE48-926C-56C6449F78A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="3500" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{23AE3EDF-41AB-D84E-9A63-204D6BF85A60}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="960" yWindow="3500" windowWidth="27640" windowHeight="16940" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>Q120</t>
-  </si>
-  <si>
-    <t>Q220</t>
-  </si>
-  <si>
-    <t>Q320</t>
-  </si>
-  <si>
-    <t>Q420</t>
-  </si>
-  <si>
-    <t>Q121</t>
-  </si>
-  <si>
-    <t>Q221</t>
-  </si>
-  <si>
-    <t>Q321</t>
-  </si>
-  <si>
-    <t>Q422</t>
-  </si>
-  <si>
-    <t>Q421</t>
-  </si>
-  <si>
-    <t>Q122</t>
-  </si>
-  <si>
-    <t>Q222</t>
-  </si>
-  <si>
-    <t>Q322</t>
-  </si>
-  <si>
-    <t>Q123</t>
-  </si>
-  <si>
-    <t>Q223</t>
-  </si>
-  <si>
-    <t>Q323</t>
-  </si>
-  <si>
-    <t>Q423</t>
-  </si>
-  <si>
-    <t>Q124</t>
-  </si>
-  <si>
-    <t>Q224</t>
-  </si>
-  <si>
-    <t>Q324</t>
-  </si>
-  <si>
-    <t>Q424</t>
-  </si>
-  <si>
-    <t>Q125</t>
-  </si>
-  <si>
-    <t>Q225</t>
-  </si>
-  <si>
-    <t>Q325</t>
-  </si>
-  <si>
-    <t>Q425</t>
-  </si>
-  <si>
-    <t>Q126</t>
-  </si>
-  <si>
-    <t>Q226</t>
-  </si>
-  <si>
-    <t>Q326</t>
-  </si>
-  <si>
-    <t>Q426</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF0563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -162,22 +52,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -608,163 +558,257 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67DDA1D6-1F4F-194C-AD5A-286704880625}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B8BD4C-DE9E-8748-AA59-C58C6E40333D}">
-  <dimension ref="B2:AV3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:AV3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="2" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V2" t="s">
-        <v>20</v>
-      </c>
-      <c r="W2" t="s">
-        <v>21</v>
-      </c>
-      <c r="X2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF2">
+    <row r="2">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Q120</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Q220</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Q320</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Q420</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Q121</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Q221</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Q321</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Q421</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Q122</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Q222</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Q322</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Q422</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Q123</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Q223</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>Q323</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>Q423</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>Q124</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>Q224</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>Q324</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>Q424</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>Q125</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>Q225</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>Q325</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>Q425</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>Q126</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>Q226</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Q326</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Q426</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
         <v>2020</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" t="n">
         <v>2021</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" t="n">
         <v>2022</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" t="n">
         <v>2023</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" t="n">
         <v>2024</v>
       </c>
-      <c r="AK2">
+      <c r="AK2" t="n">
         <v>2025</v>
       </c>
-      <c r="AL2">
+      <c r="AL2" t="n">
         <v>2026</v>
       </c>
-      <c r="AM2">
+      <c r="AM2" t="n">
         <v>2027</v>
       </c>
-      <c r="AN2">
+      <c r="AN2" t="n">
         <v>2028</v>
       </c>
-      <c r="AO2">
+      <c r="AO2" t="n">
         <v>2029</v>
       </c>
-      <c r="AP2">
+      <c r="AP2" t="n">
         <v>2030</v>
       </c>
-      <c r="AQ2">
+      <c r="AQ2" t="n">
         <v>2031</v>
       </c>
-      <c r="AR2">
+      <c r="AR2" t="n">
         <v>2032</v>
       </c>
-      <c r="AS2">
+      <c r="AS2" t="n">
         <v>2033</v>
       </c>
-      <c r="AT2">
+      <c r="AT2" t="n">
         <v>2034</v>
       </c>
-      <c r="AU2">
+      <c r="AU2" t="n">
         <v>2035</v>
       </c>
-      <c r="AV2">
+      <c r="AV2" t="n">
         <v>2036</v>
       </c>
     </row>
-    <row r="3" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>0</v>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
 </worksheet>
 </file>
--- a/LYTS.xlsx
+++ b/LYTS.xlsx
@@ -576,199 +576,775 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AV3"/>
+  <dimension ref="A1:FQ3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Q195</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Q295</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Q395</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Q495</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Q196</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Q296</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Q396</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Q496</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Q197</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Q297</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Q397</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Q497</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Q198</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Q298</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Q398</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Q498</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Q199</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Q299</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Q399</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Q499</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Q100</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Q200</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Q300</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Q400</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Q101</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Q201</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Q301</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Q401</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Q102</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Q202</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Q302</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Q402</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Q103</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Q203</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Q303</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Q403</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Q104</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Q204</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Q304</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Q404</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Q105</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Q205</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Q305</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Q405</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Q106</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Q206</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Q306</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Q406</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Q107</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Q207</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Q307</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Q407</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Q108</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Q208</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Q308</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Q408</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Q109</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Q209</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Q309</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Q409</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>Q110</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Q210</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>Q310</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>Q410</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>Q111</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>Q211</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>Q311</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>Q411</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>Q112</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>Q212</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>Q312</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>Q412</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>Q113</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>Q213</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>Q313</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>Q413</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>Q114</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>Q214</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>Q314</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>Q414</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>Q115</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>Q215</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>Q315</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>Q415</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>Q116</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>Q216</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>Q316</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>Q416</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>Q117</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>Q217</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>Q317</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>Q417</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>Q118</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>Q218</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>Q318</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Q418</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Q119</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Q219</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>Q319</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Q419</t>
+        </is>
+      </c>
+      <c r="CY2" s="1" t="inlineStr">
         <is>
           <t>Q120</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="CZ2" s="1" t="inlineStr">
         <is>
           <t>Q220</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="DA2" s="1" t="inlineStr">
         <is>
           <t>Q320</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="DB2" s="1" t="inlineStr">
         <is>
           <t>Q420</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="DC2" s="1" t="inlineStr">
         <is>
           <t>Q121</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="DD2" s="1" t="inlineStr">
         <is>
           <t>Q221</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="DE2" s="1" t="inlineStr">
         <is>
           <t>Q321</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="DF2" s="1" t="inlineStr">
         <is>
           <t>Q421</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="DG2" s="1" t="inlineStr">
         <is>
           <t>Q122</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="DH2" s="1" t="inlineStr">
         <is>
           <t>Q222</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="DI2" s="1" t="inlineStr">
         <is>
           <t>Q322</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="DJ2" s="1" t="inlineStr">
         <is>
           <t>Q422</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="DK2" s="1" t="inlineStr">
         <is>
           <t>Q123</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="DL2" s="1" t="inlineStr">
         <is>
           <t>Q223</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="DM2" s="1" t="inlineStr">
         <is>
           <t>Q323</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="DN2" s="1" t="inlineStr">
         <is>
           <t>Q423</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="DO2" s="1" t="inlineStr">
         <is>
           <t>Q124</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="DP2" s="1" t="inlineStr">
         <is>
           <t>Q224</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="DQ2" s="1" t="inlineStr">
         <is>
           <t>Q324</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="DR2" s="1" t="inlineStr">
         <is>
           <t>Q424</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="DS2" s="1" t="inlineStr">
         <is>
           <t>Q125</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="DT2" s="1" t="inlineStr">
         <is>
           <t>Q225</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="DU2" s="1" t="inlineStr">
         <is>
           <t>Q325</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="DV2" s="1" t="inlineStr">
         <is>
           <t>Q425</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="DW2" s="1" t="inlineStr">
         <is>
           <t>Q126</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="DX2" s="1" t="inlineStr">
         <is>
           <t>Q226</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>Q326</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>Q426</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="EB2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="FA2" t="n">
         <v>2020</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="FB2" t="n">
         <v>2021</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="FC2" t="n">
         <v>2022</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="FD2" t="n">
         <v>2023</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="FE2" t="n">
         <v>2024</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="FF2" t="n">
         <v>2025</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="FG2" t="n">
         <v>2026</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="FH2" t="n">
         <v>2027</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="FI2" t="n">
         <v>2028</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="FJ2" t="n">
         <v>2029</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="FK2" t="n">
         <v>2030</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="FL2" t="n">
         <v>2031</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="FM2" t="n">
         <v>2032</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="FN2" t="n">
         <v>2033</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="FO2" t="n">
         <v>2034</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="FP2" t="n">
         <v>2035</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="FQ2" t="n">
         <v>2036</v>
       </c>
     </row>
@@ -781,32 +1357,32 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CY2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CZ2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DA2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DB2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DC2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DD2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DE2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DF2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DG2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DH2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DI2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DJ2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DK2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DL2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DM2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DN2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DO2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DP2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DQ2" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DR2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DS2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DT2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DU2" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DV2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DW2" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DX2" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>

--- a/LYTS.xlsx
+++ b/LYTS.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -28,6 +28,13 @@
     <font>
       <name val="Aptos Narrow"/>
       <color rgb="FF0563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <i val="1"/>
+      <color rgb="FF7030A0"/>
       <sz val="12"/>
       <u val="single"/>
     </font>
@@ -52,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,507 +584,506 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ3"/>
+  <dimension ref="A2:FQ3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Q195</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Q295</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Q395</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Q495</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Q196</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Q296</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Q396</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Q496</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Q197</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Q297</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Q397</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Q497</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Q198</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Q298</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Q398</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Q498</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Q199</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Q299</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Q399</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Q499</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Q100</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Q200</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Q300</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Q400</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Q101</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>Q201</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>Q301</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>Q401</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Q102</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>Q202</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Q302</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>Q402</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" s="1" t="inlineStr">
         <is>
           <t>Q103</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" s="1" t="inlineStr">
         <is>
           <t>Q203</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" s="1" t="inlineStr">
         <is>
           <t>Q303</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AL2" s="1" t="inlineStr">
         <is>
           <t>Q403</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AM2" s="1" t="inlineStr">
         <is>
           <t>Q104</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AN2" s="1" t="inlineStr">
         <is>
           <t>Q204</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AO2" s="1" t="inlineStr">
         <is>
           <t>Q304</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AP2" s="1" t="inlineStr">
         <is>
           <t>Q404</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AQ2" s="1" t="inlineStr">
         <is>
           <t>Q105</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AR2" s="1" t="inlineStr">
         <is>
           <t>Q205</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" s="1" t="inlineStr">
         <is>
           <t>Q305</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT2" s="1" t="inlineStr">
         <is>
           <t>Q405</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>Q106</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AV2" s="1" t="inlineStr">
         <is>
           <t>Q206</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>Q306</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX2" s="1" t="inlineStr">
         <is>
           <t>Q406</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>Q107</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ2" s="1" t="inlineStr">
         <is>
           <t>Q207</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BA2" s="1" t="inlineStr">
         <is>
           <t>Q307</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" s="1" t="inlineStr">
         <is>
           <t>Q407</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BC2" s="1" t="inlineStr">
         <is>
           <t>Q108</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BD2" s="1" t="inlineStr">
         <is>
           <t>Q208</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BE2" s="1" t="inlineStr">
         <is>
           <t>Q308</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF2" s="1" t="inlineStr">
         <is>
           <t>Q408</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BG2" s="1" t="inlineStr">
         <is>
           <t>Q109</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BH2" s="1" t="inlineStr">
         <is>
           <t>Q209</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BI2" s="1" t="inlineStr">
         <is>
           <t>Q309</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ2" s="1" t="inlineStr">
         <is>
           <t>Q409</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK2" s="1" t="inlineStr">
         <is>
           <t>Q110</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BL2" s="1" t="inlineStr">
         <is>
           <t>Q210</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BM2" s="1" t="inlineStr">
         <is>
           <t>Q310</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN2" s="1" t="inlineStr">
         <is>
           <t>Q410</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO2" s="1" t="inlineStr">
         <is>
           <t>Q111</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BP2" s="1" t="inlineStr">
         <is>
           <t>Q211</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BQ2" s="1" t="inlineStr">
         <is>
           <t>Q311</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BR2" s="1" t="inlineStr">
         <is>
           <t>Q411</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BS2" s="1" t="inlineStr">
         <is>
           <t>Q112</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BT2" s="1" t="inlineStr">
         <is>
           <t>Q212</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BU2" s="1" t="inlineStr">
         <is>
           <t>Q312</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BV2" s="1" t="inlineStr">
         <is>
           <t>Q412</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BW2" s="1" t="inlineStr">
         <is>
           <t>Q113</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BX2" s="1" t="inlineStr">
         <is>
           <t>Q213</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BY2" s="1" t="inlineStr">
         <is>
           <t>Q313</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="BZ2" s="1" t="inlineStr">
         <is>
           <t>Q413</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CA2" s="1" t="inlineStr">
         <is>
           <t>Q114</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB2" s="1" t="inlineStr">
         <is>
           <t>Q214</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CC2" s="1" t="inlineStr">
         <is>
           <t>Q314</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CD2" s="1" t="inlineStr">
         <is>
           <t>Q414</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CE2" s="1" t="inlineStr">
         <is>
           <t>Q115</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CF2" s="1" t="inlineStr">
         <is>
           <t>Q215</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CG2" s="1" t="inlineStr">
         <is>
           <t>Q315</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CH2" s="1" t="inlineStr">
         <is>
           <t>Q415</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI2" s="1" t="inlineStr">
         <is>
           <t>Q116</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CJ2" s="1" t="inlineStr">
         <is>
           <t>Q216</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CK2" s="1" t="inlineStr">
         <is>
           <t>Q316</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CL2" s="1" t="inlineStr">
         <is>
           <t>Q416</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CM2" s="1" t="inlineStr">
         <is>
           <t>Q117</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CN2" s="1" t="inlineStr">
         <is>
           <t>Q217</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CO2" s="1" t="inlineStr">
         <is>
           <t>Q317</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CP2" s="1" t="inlineStr">
         <is>
           <t>Q417</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CQ2" s="1" t="inlineStr">
         <is>
           <t>Q118</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CR2" s="1" t="inlineStr">
         <is>
           <t>Q218</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CS2" s="1" t="inlineStr">
         <is>
           <t>Q318</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CT2" s="1" t="inlineStr">
         <is>
           <t>Q418</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CU2" s="1" t="inlineStr">
         <is>
           <t>Q119</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CV2" s="1" t="inlineStr">
         <is>
           <t>Q219</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CW2" s="1" t="inlineStr">
         <is>
           <t>Q319</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CX2" s="1" t="inlineStr">
         <is>
           <t>Q419</t>
         </is>
@@ -1357,34 +1364,134 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CY2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CZ2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DA2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DB2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DC2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DD2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DE2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DF2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DG2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DH2" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DI2" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DJ2" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DK2" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DL2" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DM2" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DN2" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DO2" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DP2" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DQ2" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DR2" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DS2" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DT2" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DU2" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DV2" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DW2" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DX2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG2" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH2" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI2" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ2" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK2" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL2" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM2" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN2" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP2" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ2" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR2" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS2" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT2" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU2" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV2" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW2" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX2" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY2" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA2" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB2" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC2" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD2" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE2" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF2" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG2" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH2" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI2" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ2" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK2" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL2" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CM2" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CN2" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CO2" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CP2" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CQ2" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CR2" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CS2" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CT2" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CU2" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CV2" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CW2" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CX2" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CY2" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CZ2" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DA2" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DB2" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DC2" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DD2" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DE2" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DF2" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DG2" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DH2" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DI2" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DJ2" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DK2" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DL2" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DM2" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DN2" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DO2" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DP2" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DQ2" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DR2" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DS2" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DT2" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DU2" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DV2" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DW2" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DX2" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId127"/>
 </worksheet>
 </file>
--- a/LYTS.xlsx
+++ b/LYTS.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -36,6 +36,12 @@
       <i val="1"/>
       <color rgb="FF7030A0"/>
       <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -59,10 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -143,33 +150,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
+      <xdr:col>128</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>128</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6034B925-50E7-A3CC-FAE6-8C775CCD7564}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23139400" y="63500"/>
-          <a:ext cx="0" cy="8267700"/>
-        </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
@@ -196,33 +193,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
+      <xdr:col>162</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>162</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CEFFD1E-95F6-BC41-B05B-5DB09CB2C836}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="31394400" y="63500"/>
-          <a:ext cx="0" cy="8267700"/>
-        </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
@@ -584,9 +571,641 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:FQ3"/>
+  <dimension ref="A1:FQ3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
+    <row r="1">
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>10-K405</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>10-K405</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>10-K405</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>10-K405</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>10-K405</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AY1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="AZ1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BA1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BB1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BC1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BD1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BE1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BF1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BG1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BH1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BI1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BJ1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BK1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BL1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BM1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BN1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BO1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BP1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BQ1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BR1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BS1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BT1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BU1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BV1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BW1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BX1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="BY1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="BZ1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CA1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CB1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CC1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CD1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CE1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CF1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CG1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CH1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CI1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CJ1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CK1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CL1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CM1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CN1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CO1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CP1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CQ1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CR1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CS1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CT1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CU1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CV1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="CW1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CX1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CY1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="CZ1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="DA1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DB1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DC1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DD1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="DE1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DF1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DG1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DH1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="DI1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DJ1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DK1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DL1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="DM1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DN1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DO1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DP1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="DQ1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DR1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DS1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DT1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="DU1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DV1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DW1" s="3" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="DX1" s="3" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -1364,134 +1983,260 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG2" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH2" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI2" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ2" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK2" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL2" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM2" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN2" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP2" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ2" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR2" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS2" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT2" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU2" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV2" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW2" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX2" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY2" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA2" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB2" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC2" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD2" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE2" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF2" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG2" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH2" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI2" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ2" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK2" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL2" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CM2" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CN2" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CO2" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CP2" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CQ2" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CR2" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CS2" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CT2" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CU2" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CV2" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CW2" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CX2" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CY2" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CZ2" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DA2" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DB2" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DC2" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DD2" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DE2" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DF2" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DG2" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DH2" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DI2" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DJ2" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DK2" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DL2" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DM2" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DN2" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DO2" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DP2" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DQ2" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DR2" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DS2" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DT2" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DU2" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DV2" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DW2" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DX2" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G1" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I1" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K1" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P1" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q1" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R1" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S1" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T1" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U1" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V1" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W1" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X1" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y1" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z1" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA1" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB1" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC1" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD1" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE1" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF1" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG1" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH1" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI1" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ1" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK1" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL1" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM1" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN1" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO1" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP1" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ1" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR1" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS1" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT1" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU1" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV1" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW1" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX1" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY1" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ1" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA1" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB1" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC1" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD1" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE1" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF1" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG1" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH1" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI1" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ1" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK1" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL1" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM1" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN1" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO1" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP1" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ1" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR1" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS1" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT1" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU1" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV1" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW1" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX1" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY1" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ1" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA1" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB1" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC1" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD1" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE1" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF1" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG1" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH1" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI1" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ1" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK1" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL1" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CM1" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CN1" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CO1" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CP1" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CQ1" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CR1" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CS1" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CT1" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CU1" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CV1" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CW1" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CX1" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CY1" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CZ1" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DA1" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DB1" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DC1" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DD1" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DE1" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DF1" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DG1" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DH1" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DI1" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DJ1" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DK1" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DL1" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DM1" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DN1" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DO1" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DP1" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DQ1" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DR1" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DS1" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DT1" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DU1" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DV1" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DW1" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DX1" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AC2" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AE2" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF2" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AG2" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AH2" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AI2" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AJ2" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AK2" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL2" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AM2" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AN2" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AO2" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AP2" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AQ2" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AR2" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AS2" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AT2" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AU2" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AV2" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AW2" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AX2" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AY2" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BA2" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BB2" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BC2" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BD2" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BE2" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BF2" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BG2" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BH2" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BI2" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BJ2" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BK2" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BL2" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BM2" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BN2" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BO2" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BP2" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BQ2" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BR2" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BS2" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BU2" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BV2" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BW2" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BX2" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BY2" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BZ2" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CA2" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CB2" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CC2" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CD2" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CE2" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CF2" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CG2" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CH2" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CI2" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CJ2" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CK2" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CL2" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CM2" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CN2" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CO2" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CP2" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CQ2" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CR2" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CS2" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CT2" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CU2" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CV2" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CW2" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CX2" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CY2" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="CZ2" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DA2" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DB2" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DC2" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DD2" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DE2" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DF2" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DG2" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DH2" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DI2" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DJ2" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DK2" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DL2" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DM2" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DN2" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DO2" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DP2" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DQ2" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DR2" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DS2" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DT2" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DU2" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DV2" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DW2" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="DX2" r:id="rId252"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId127"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId253"/>
 </worksheet>
 </file>